--- a/AAII_Financials/Quarterly/JWSM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JWSM_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Quarterly/JWSM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JWSM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="92">
   <si>
     <t>JWSM</t>
   </si>
@@ -656,78 +656,79 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
@@ -740,8 +741,14 @@
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -796,8 +803,14 @@
       <c r="T8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3">
+        <v>0</v>
+      </c>
+      <c r="V8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -852,8 +865,14 @@
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -908,8 +927,14 @@
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -930,8 +955,10 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -986,8 +1013,14 @@
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1042,50 +1075,56 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
+        <v>700</v>
+      </c>
+      <c r="F14" s="3">
         <v>-700</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>-1200</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>1200</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1098,8 +1137,14 @@
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1154,8 +1199,14 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1173,50 +1224,52 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>600</v>
+      </c>
+      <c r="E17" s="3">
+        <v>700</v>
+      </c>
+      <c r="F17" s="3">
         <v>-300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>-1100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>-900</v>
-      </c>
-      <c r="I17" s="3">
-        <v>500</v>
-      </c>
-      <c r="J17" s="3">
-        <v>4500</v>
       </c>
       <c r="K17" s="3">
         <v>500</v>
       </c>
       <c r="L17" s="3">
+        <v>4500</v>
+      </c>
+      <c r="M17" s="3">
+        <v>500</v>
+      </c>
+      <c r="N17" s="3">
         <v>400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>1400</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1229,8 +1282,14 @@
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1238,41 +1297,41 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F18" s="3">
+        <v>300</v>
+      </c>
+      <c r="G18" s="3">
         <v>-200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>1100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>900</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-500</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-4500</v>
       </c>
       <c r="K18" s="3">
         <v>-500</v>
       </c>
       <c r="L18" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="M18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="N18" s="3">
         <v>-400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-1400</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1285,8 +1344,14 @@
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1307,8 +1372,10 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1316,41 +1383,41 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>200</v>
+      </c>
+      <c r="F20" s="3">
+        <v>900</v>
+      </c>
+      <c r="G20" s="3">
         <v>2400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>3100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>8600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>10200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>10500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>20300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>4500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>4300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-3700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-11300</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1363,8 +1430,14 @@
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1386,27 +1459,27 @@
       <c r="I21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J21" s="3">
+      <c r="J21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L21" s="3">
         <v>15800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>4000</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="3">
         <v>-12600</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1419,8 +1492,14 @@
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1475,50 +1554,56 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F23" s="3">
         <v>1200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>2200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>2400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>9700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>11200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>10000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>15800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>4000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>3900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-4100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-12600</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1531,8 +1616,14 @@
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1587,8 +1678,14 @@
       <c r="T24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1643,50 +1740,56 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F26" s="3">
         <v>1200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>2200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>2400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>9700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>11200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>10000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>15800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>4000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>3900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-4100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-12600</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1699,50 +1802,56 @@
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F27" s="3">
         <v>1200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>2200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>2400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>9700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>11200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>10000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>15800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>4000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>3900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-4100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-12600</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1755,8 +1864,14 @@
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1811,8 +1926,14 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1867,8 +1988,14 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1923,8 +2050,14 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1979,8 +2112,14 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1988,41 +2127,41 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F32" s="3">
+        <v>-900</v>
+      </c>
+      <c r="G32" s="3">
         <v>-2400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-3100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-8600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-10200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-10500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-20300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-4500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-4300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>3700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>11300</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2035,50 +2174,56 @@
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F33" s="3">
         <v>1200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>2200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>2400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>9700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>11200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>10000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>15800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>4000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>3900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-4100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-12600</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2091,8 +2236,14 @@
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2147,50 +2298,56 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F35" s="3">
         <v>1200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>2200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>2400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>9700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>11200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>10000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>15800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>4000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>3900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-4100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-12600</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2203,55 +2360,61 @@
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2264,8 +2427,14 @@
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2286,8 +2455,10 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2308,50 +2479,52 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>300</v>
+      </c>
+      <c r="E41" s="3">
         <v>200</v>
       </c>
-      <c r="E41" s="3">
-        <v>0</v>
-      </c>
       <c r="F41" s="3">
+        <v>200</v>
+      </c>
+      <c r="G41" s="3">
+        <v>0</v>
+      </c>
+      <c r="H41" s="3">
         <v>100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>1200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>1400</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2364,8 +2537,14 @@
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2420,8 +2599,14 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2476,8 +2661,14 @@
       <c r="T43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+      <c r="V43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2532,8 +2723,14 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2541,41 +2738,41 @@
         <v>100</v>
       </c>
       <c r="E45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F45" s="3">
         <v>100</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H45" s="3">
         <v>100</v>
       </c>
       <c r="I45" s="3">
+        <v>0</v>
+      </c>
+      <c r="J45" s="3">
+        <v>100</v>
+      </c>
+      <c r="K45" s="3">
         <v>300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>600</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2588,8 +2785,14 @@
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2597,7 +2800,7 @@
         <v>300</v>
       </c>
       <c r="E46" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F46" s="3">
         <v>300</v>
@@ -2609,29 +2812,29 @@
         <v>300</v>
       </c>
       <c r="I46" s="3">
+        <v>100</v>
+      </c>
+      <c r="J46" s="3">
+        <v>300</v>
+      </c>
+      <c r="K46" s="3">
         <v>600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>1200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>1500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>1700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>2000</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2644,50 +2847,56 @@
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>15600</v>
+      </c>
+      <c r="E47" s="3">
+        <v>23000</v>
+      </c>
+      <c r="F47" s="3">
         <v>22800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>22600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>22400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>1050300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>1041600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>1037000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>1035400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>1035200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>1035100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>1035000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>1035000</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2700,8 +2909,14 @@
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2756,8 +2971,14 @@
       <c r="T48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3">
+        <v>0</v>
+      </c>
+      <c r="V48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2812,8 +3033,14 @@
       <c r="T49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+      <c r="V49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2868,8 +3095,14 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2924,8 +3157,14 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2980,8 +3219,14 @@
       <c r="T52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3">
+        <v>0</v>
+      </c>
+      <c r="V52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3036,50 +3281,56 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E54" s="3">
+        <v>23200</v>
+      </c>
+      <c r="F54" s="3">
         <v>23100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>22700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>22700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>1050500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>1041900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>1037500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>1036200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>1036400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>1036600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>1036700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>1037000</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3092,8 +3343,14 @@
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3114,8 +3371,10 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3136,8 +3395,10 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3165,21 +3426,21 @@
       <c r="K57" s="3">
         <v>0</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
+      <c r="L57" s="3">
+        <v>0</v>
       </c>
       <c r="M57" s="3">
+        <v>0</v>
+      </c>
+      <c r="N57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O57" s="3">
         <v>300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>200</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3192,8 +3453,14 @@
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3248,49 +3515,55 @@
       <c r="T58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>3500</v>
+        <v>4600</v>
       </c>
       <c r="E59" s="3">
         <v>4100</v>
       </c>
       <c r="F59" s="3">
+        <v>3500</v>
+      </c>
+      <c r="G59" s="3">
         <v>4100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
+        <v>4100</v>
+      </c>
+      <c r="I59" s="3">
         <v>3800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>3900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>5100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>4800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>400</v>
       </c>
-      <c r="M59" s="3">
-        <v>0</v>
-      </c>
-      <c r="N59" s="3">
-        <v>0</v>
-      </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
+      <c r="O59" s="3">
+        <v>0</v>
+      </c>
+      <c r="P59" s="3">
+        <v>0</v>
       </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
@@ -3298,56 +3571,62 @@
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S59" s="3">
-        <v>0</v>
-      </c>
-      <c r="T59" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U59" s="3">
+        <v>0</v>
+      </c>
+      <c r="V59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>3500</v>
+        <v>4600</v>
       </c>
       <c r="E60" s="3">
         <v>4100</v>
       </c>
       <c r="F60" s="3">
+        <v>3500</v>
+      </c>
+      <c r="G60" s="3">
         <v>4100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
+        <v>4100</v>
+      </c>
+      <c r="I60" s="3">
         <v>3800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>3900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>5100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>4800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>200</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3360,26 +3639,32 @@
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E61" s="3">
         <v>1000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G61" s="3">
         <v>500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>500</v>
       </c>
-      <c r="G61" s="3">
-        <v>0</v>
-      </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
       <c r="I61" s="3">
         <v>0</v>
       </c>
@@ -3416,50 +3701,56 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E62" s="3">
         <v>1500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
+        <v>1500</v>
+      </c>
+      <c r="G62" s="3">
         <v>16400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>18600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>38800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>39900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>45500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>54500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>74600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>79000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>83200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>79500</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3472,8 +3763,14 @@
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3528,8 +3825,14 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3584,8 +3887,14 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3640,50 +3949,56 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>14200</v>
+      </c>
+      <c r="E66" s="3">
+        <v>6600</v>
+      </c>
+      <c r="F66" s="3">
         <v>6000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>21000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>23200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>42600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>43900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>50600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>59300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>75300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>79500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>83500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>79700</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3696,8 +4011,14 @@
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3718,8 +4039,10 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3774,8 +4097,14 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3830,8 +4159,14 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3886,8 +4221,14 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3942,50 +4283,56 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-13800</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="F72" s="3">
         <v>-5700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-20900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-22900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-42500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-43500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-50000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-58100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-73900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-77900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-16700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-12600</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3998,8 +4345,14 @@
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4054,8 +4407,14 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4110,8 +4469,14 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4166,50 +4531,56 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E76" s="3">
+        <v>16600</v>
+      </c>
+      <c r="F76" s="3">
         <v>17100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>1700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>-500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>1007800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>998100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>986900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>976900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>961100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>957100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>953200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>957300</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4222,8 +4593,14 @@
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4278,55 +4655,61 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4339,50 +4722,56 @@
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F81" s="3">
         <v>1200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>2200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>2400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>9700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>11200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>10000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>15800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>4000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>3900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-4100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-12600</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4395,8 +4784,14 @@
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4417,8 +4812,10 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4473,8 +4870,14 @@
       <c r="T83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4529,8 +4932,14 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4585,8 +4994,14 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4641,8 +5056,14 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4697,8 +5118,14 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4753,50 +5180,56 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E89" s="3">
+        <v>0</v>
+      </c>
+      <c r="F89" s="3">
         <v>-300</v>
-      </c>
-      <c r="E89" s="3">
-        <v>-100</v>
-      </c>
-      <c r="F89" s="3">
-        <v>-500</v>
       </c>
       <c r="G89" s="3">
         <v>-100</v>
       </c>
       <c r="H89" s="3">
+        <v>-500</v>
+      </c>
+      <c r="I89" s="3">
         <v>-100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K89" s="3">
         <v>-200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-100</v>
       </c>
-      <c r="M89" s="3">
-        <v>0</v>
-      </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
+        <v>0</v>
+      </c>
+      <c r="P89" s="3">
         <v>-700</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4809,8 +5242,14 @@
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4831,8 +5270,10 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4887,8 +5328,14 @@
       <c r="T91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4943,8 +5390,14 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4999,26 +5452,32 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>7600</v>
       </c>
       <c r="E94" s="3">
         <v>0</v>
       </c>
       <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
         <v>1032000</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
       <c r="I94" s="3">
         <v>0</v>
       </c>
@@ -5035,14 +5494,14 @@
         <v>0</v>
       </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
         <v>-1035000</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5055,8 +5514,14 @@
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5077,8 +5542,10 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5133,8 +5600,14 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5189,8 +5662,14 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5245,8 +5724,14 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5301,26 +5786,32 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>500</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>-1031500</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
         <v>0</v>
       </c>
@@ -5337,14 +5828,14 @@
         <v>0</v>
       </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>1037100</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5357,8 +5848,14 @@
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5413,50 +5910,56 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>100</v>
+      </c>
+      <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>200</v>
-      </c>
-      <c r="E102" s="3">
-        <v>-100</v>
-      </c>
-      <c r="F102" s="3">
-        <v>0</v>
       </c>
       <c r="G102" s="3">
         <v>-100</v>
       </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>-100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K102" s="3">
         <v>-200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-100</v>
       </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3">
         <v>1400</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5467,6 +5970,12 @@
         <v>3</v>
       </c>
       <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/JWSM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JWSM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="92">
   <si>
     <t>JWSM</t>
   </si>
@@ -656,82 +656,83 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
@@ -747,8 +748,11 @@
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -809,8 +813,11 @@
       <c r="V8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -871,8 +878,11 @@
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -933,8 +943,11 @@
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -957,8 +970,9 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1019,8 +1033,11 @@
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1081,40 +1098,43 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-700</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>-1200</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1123,11 +1143,11 @@
         <v>0</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>1200</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1143,8 +1163,11 @@
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1205,8 +1228,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1226,53 +1252,54 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>300</v>
+      </c>
+      <c r="E17" s="3">
         <v>600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>-300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>-1100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>-900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>500</v>
-      </c>
-      <c r="N17" s="3">
-        <v>400</v>
       </c>
       <c r="O17" s="3">
         <v>400</v>
       </c>
       <c r="P17" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q17" s="3">
         <v>1400</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1288,8 +1315,11 @@
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1297,44 +1327,44 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-600</v>
+      </c>
+      <c r="F18" s="3">
         <v>-700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-4500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-500</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-400</v>
       </c>
       <c r="O18" s="3">
         <v>-400</v>
       </c>
       <c r="P18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="Q18" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1350,8 +1380,11 @@
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1374,8 +1407,9 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1383,44 +1417,44 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="F20" s="3">
         <v>200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>3100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>8600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>10200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>10500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>20300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>4500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>4300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-3700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-11300</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1436,8 +1470,11 @@
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1465,24 +1502,24 @@
       <c r="K21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L21" s="3">
+      <c r="L21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M21" s="3">
         <v>15800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>4000</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3">
         <v>-12600</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1498,8 +1535,11 @@
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1560,53 +1600,56 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-7200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>9700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>11200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>10000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>15800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>4000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-4100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-12600</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1622,8 +1665,11 @@
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1684,8 +1730,11 @@
       <c r="V24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1746,53 +1795,56 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-7200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>2400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>9700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>11200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>10000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>15800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>4000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>3900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-4100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-12600</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1808,53 +1860,56 @@
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-7200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>2400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>9700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>11200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>10000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>15800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>4000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-4100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-12600</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1870,8 +1925,11 @@
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1932,8 +1990,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1994,8 +2055,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2056,8 +2120,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2118,8 +2185,11 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2127,44 +2197,44 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>6500</v>
+      </c>
+      <c r="F32" s="3">
         <v>-200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-3100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-8600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-10200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-10500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-20300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-4500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-4300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>3700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>11300</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2180,53 +2250,56 @@
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-7200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>2400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>9700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>11200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>10000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>15800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>4000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-4100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-12600</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2242,8 +2315,11 @@
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2304,53 +2380,56 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-7200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>2400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>9700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>11200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>10000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>15800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>4000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-4100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-12600</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2366,58 +2445,61 @@
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2433,8 +2515,11 @@
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2457,8 +2542,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2481,53 +2567,54 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>0</v>
+      </c>
+      <c r="E41" s="3">
         <v>300</v>
-      </c>
-      <c r="E41" s="3">
-        <v>200</v>
       </c>
       <c r="F41" s="3">
         <v>200</v>
       </c>
       <c r="G41" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I41" s="3">
         <v>100</v>
       </c>
       <c r="J41" s="3">
+        <v>100</v>
+      </c>
+      <c r="K41" s="3">
         <v>200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1400</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2543,8 +2630,11 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2605,8 +2695,11 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2667,8 +2760,11 @@
       <c r="V43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2729,8 +2825,11 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2738,10 +2837,10 @@
         <v>100</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G45" s="3">
         <v>100</v>
@@ -2750,32 +2849,32 @@
         <v>100</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J45" s="3">
+        <v>0</v>
+      </c>
+      <c r="K45" s="3">
         <v>100</v>
-      </c>
-      <c r="K45" s="3">
-        <v>300</v>
       </c>
       <c r="L45" s="3">
         <v>300</v>
       </c>
       <c r="M45" s="3">
+        <v>300</v>
+      </c>
+      <c r="N45" s="3">
         <v>100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>600</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2791,53 +2890,56 @@
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>100</v>
+      </c>
+      <c r="E46" s="3">
         <v>300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2000</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2853,52 +2955,55 @@
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>15800</v>
+      </c>
+      <c r="E47" s="3">
         <v>15600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>23000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>22800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>22600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>22400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1050300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1041600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1037000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1035400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1035200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1035100</v>
-      </c>
-      <c r="O47" s="3">
-        <v>1035000</v>
       </c>
       <c r="P47" s="3">
         <v>1035000</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
+      <c r="Q47" s="3">
+        <v>1035000</v>
       </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
@@ -2915,8 +3020,11 @@
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2977,8 +3085,11 @@
       <c r="V48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3039,8 +3150,11 @@
       <c r="V49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3101,8 +3215,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3163,8 +3280,11 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3225,8 +3345,11 @@
       <c r="V52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3287,8 +3410,11 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -3296,44 +3422,44 @@
         <v>15900</v>
       </c>
       <c r="E54" s="3">
+        <v>15900</v>
+      </c>
+      <c r="F54" s="3">
         <v>23200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>23100</v>
-      </c>
-      <c r="G54" s="3">
-        <v>22700</v>
       </c>
       <c r="H54" s="3">
         <v>22700</v>
       </c>
       <c r="I54" s="3">
+        <v>22700</v>
+      </c>
+      <c r="J54" s="3">
         <v>1050500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1041900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1037500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1036200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1036400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1036600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1036700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1037000</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3349,8 +3475,11 @@
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3373,8 +3502,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3397,8 +3527,9 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3432,18 +3563,18 @@
       <c r="M57" s="3">
         <v>0</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O57" s="3">
+      <c r="N57" s="3">
+        <v>0</v>
+      </c>
+      <c r="O57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P57" s="3">
         <v>300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>200</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3459,8 +3590,11 @@
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3521,52 +3655,55 @@
       <c r="V58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E59" s="3">
         <v>4600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3500</v>
-      </c>
-      <c r="G59" s="3">
-        <v>4100</v>
       </c>
       <c r="H59" s="3">
         <v>4100</v>
       </c>
       <c r="I59" s="3">
+        <v>4100</v>
+      </c>
+      <c r="J59" s="3">
         <v>3800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>5100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>400</v>
       </c>
-      <c r="O59" s="3">
-        <v>0</v>
-      </c>
       <c r="P59" s="3">
         <v>0</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
+      <c r="Q59" s="3">
+        <v>0</v>
       </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
@@ -3577,59 +3714,62 @@
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U59" s="3">
-        <v>0</v>
+      <c r="U59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E60" s="3">
         <v>4600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3500</v>
-      </c>
-      <c r="G60" s="3">
-        <v>4100</v>
       </c>
       <c r="H60" s="3">
         <v>4100</v>
       </c>
       <c r="I60" s="3">
+        <v>4100</v>
+      </c>
+      <c r="J60" s="3">
         <v>3800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>200</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3645,8 +3785,11 @@
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3654,19 +3797,19 @@
         <v>1400</v>
       </c>
       <c r="E61" s="3">
-        <v>1000</v>
+        <v>1400</v>
       </c>
       <c r="F61" s="3">
         <v>1000</v>
       </c>
       <c r="G61" s="3">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="H61" s="3">
         <v>500</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="J61" s="3">
         <v>0</v>
@@ -3707,53 +3850,56 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E62" s="3">
         <v>8200</v>
-      </c>
-      <c r="E62" s="3">
-        <v>1500</v>
       </c>
       <c r="F62" s="3">
         <v>1500</v>
       </c>
       <c r="G62" s="3">
+        <v>1500</v>
+      </c>
+      <c r="H62" s="3">
         <v>16400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>18600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>38800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>39900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>45500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>54500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>74600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>79000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>83200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>79500</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3769,8 +3915,11 @@
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3831,8 +3980,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3893,8 +4045,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3955,53 +4110,56 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E66" s="3">
         <v>14200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>6600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>21000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>23200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>42600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>43900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>50600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>59300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>75300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>79500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>83500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>79700</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4017,8 +4175,11 @@
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4041,8 +4202,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4103,8 +4265,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4165,8 +4330,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4227,8 +4395,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4289,53 +4460,56 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-13800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-6400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-5700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-20900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-22900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-42500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-43500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-50000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-58100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-73900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-77900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-16700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-12600</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4351,8 +4525,11 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4413,8 +4590,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4475,8 +4655,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4537,53 +4720,56 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E76" s="3">
         <v>1700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>16600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>17100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1007800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>998100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>986900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>976900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>961100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>957100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>953200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>957300</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4599,8 +4785,11 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4661,58 +4850,61 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4728,53 +4920,56 @@
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-7200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>2400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>9700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>11200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>10000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>15800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>4000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-4100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-12600</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4790,8 +4985,11 @@
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4814,8 +5012,9 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4876,8 +5075,11 @@
       <c r="V83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4938,8 +5140,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5000,8 +5205,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5062,8 +5270,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5124,8 +5335,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5186,53 +5400,56 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-200</v>
       </c>
-      <c r="E89" s="3">
-        <v>0</v>
-      </c>
       <c r="F89" s="3">
+        <v>0</v>
+      </c>
+      <c r="G89" s="3">
         <v>-300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-500</v>
-      </c>
-      <c r="I89" s="3">
-        <v>-100</v>
       </c>
       <c r="J89" s="3">
         <v>-100</v>
       </c>
       <c r="K89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L89" s="3">
         <v>-200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-600</v>
-      </c>
-      <c r="M89" s="3">
-        <v>-100</v>
       </c>
       <c r="N89" s="3">
         <v>-100</v>
       </c>
       <c r="O89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="3">
         <v>-700</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5248,8 +5465,11 @@
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5272,8 +5492,9 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5334,8 +5555,11 @@
       <c r="V91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5396,8 +5620,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5458,17 +5685,20 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E94" s="3">
         <v>7600</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
       <c r="F94" s="3">
         <v>0</v>
       </c>
@@ -5476,11 +5706,11 @@
         <v>0</v>
       </c>
       <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
         <v>1032000</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
       <c r="J94" s="3">
         <v>0</v>
       </c>
@@ -5500,11 +5730,11 @@
         <v>0</v>
       </c>
       <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-1035000</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5520,8 +5750,11 @@
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5544,8 +5777,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5606,8 +5840,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5668,8 +5905,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5730,8 +5970,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5792,29 +6035,32 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>-7300</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>500</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>-1031500</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
         <v>0</v>
       </c>
@@ -5834,11 +6080,11 @@
         <v>0</v>
       </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>1037100</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5854,8 +6100,11 @@
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5916,53 +6165,56 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E102" s="3">
         <v>100</v>
       </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-100</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
       <c r="I102" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J102" s="3">
         <v>-100</v>
       </c>
       <c r="K102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L102" s="3">
         <v>-200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-600</v>
-      </c>
-      <c r="M102" s="3">
-        <v>-100</v>
       </c>
       <c r="N102" s="3">
         <v>-100</v>
       </c>
       <c r="O102" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3">
         <v>1400</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5976,6 +6228,9 @@
         <v>3</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
